--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -777,56 +777,65 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119829963</v>
+        <v>129151971</v>
       </c>
       <c r="B3" t="n">
-        <v>89239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>245031</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappungsmyren, Lappungsmyren, Jmt</t>
+          <t>Lappungsmyren (leden), Ankarede, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>466006</v>
+        <v>465175</v>
       </c>
       <c r="R3" t="n">
-        <v>7187688</v>
+        <v>7187535</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,17 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>I urskogsartad fjällgranskog. På själva växtplatsen finns väldigt lite indikationer på någon form av kalkpåverkan. Bärriset är utglesat och består av blåbär med spridda förekomster av ripbär, lingon och någon ekbräken. Av skogen som kollades igenom sågs inga tecken på kalkpåverkan och inga andra kalkknutna marksvampar sågs. Är svampen kanske hellre knuten till äldre barrskogar med lång kontinuitet än strikta kalkgranskogar?</t>
+          <t>Strax O. lokalpunkt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,15 +885,240 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129151847</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57827</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lappungsmyren (leden), Ankarede, Frostviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465175</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7187535</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lockande strax N. leden.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119829963</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89239</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lappungsmyren, Lappungsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>466006</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7187688</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I urskogsartad fjällgranskog. På själva växtplatsen finns väldigt lite indikationer på någon form av kalkpåverkan. Bärriset är utglesat och består av blåbär med spridda förekomster av ripbär, lingon och någon ekbräken. Av skogen som kollades igenom sågs inga tecken på kalkpåverkan och inga andra kalkknutna marksvampar sågs. Är svampen kanske hellre knuten till äldre barrskogar med lång kontinuitet än strikta kalkgranskogar?</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129151971</v>
       </c>
       <c r="B3" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129151847</v>
       </c>
       <c r="B4" t="n">
-        <v>57827</v>
+        <v>57829</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129151971</v>
       </c>
       <c r="B3" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129151847</v>
       </c>
       <c r="B4" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129151971</v>
       </c>
       <c r="B3" t="n">
-        <v>58586</v>
+        <v>58589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>129151847</v>
       </c>
       <c r="B4" t="n">
-        <v>57831</v>
+        <v>57834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,12 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>89239</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I urskogsartad fjällgranskog. På själva växtplatsen finns väldigt lite indikationer på någon form av kalkpåverkan. Bärriset är utglesat och består av blåbär med spridda förekomster av ripbär, lingon och någon ekbräken. Av skogen som kollades igenom sågs inga tecken på kalkpåverkan och inga andra kalkknutna marksvampar sågs. Är svampen kanske hellre knuten till äldre barrskogar med lång kontinuitet än strikta kalkgranskogar?</t>
+          <t>I urskogsartad fjällgranskog.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>90372</v>
+        <v>90375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>90375</v>
+        <v>90376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>90376</v>
+        <v>90393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>90409</v>
+        <v>90411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>119829963</v>
       </c>
       <c r="B5" t="n">
-        <v>90411</v>
+        <v>90497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>119828801</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,65 +772,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129151971</v>
+        <v>86939718</v>
       </c>
       <c r="B3" t="n">
-        <v>58589</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lappungsmyren (leden), Ankarede, Frostviken, Jmt</t>
+          <t>Rastplats längs leden., Ankarede, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>465175</v>
+        <v>465418</v>
       </c>
       <c r="R3" t="n">
-        <v>7187535</v>
+        <v>7187488</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,17 +849,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Strax O. lokalpunkt.</t>
+          <t>2020-07-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,11 +894,11 @@
         <v>129151847</v>
       </c>
       <c r="B4" t="n">
-        <v>57834</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1011,51 +1005,65 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119829963</v>
+        <v>129151971</v>
       </c>
       <c r="B5" t="n">
-        <v>90496</v>
+        <v>58817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>245031</v>
+        <v>208249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Borgsjömusseron</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma borgsjoeënse</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Jacobsson &amp; Muskos</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappungsmyren, Lappungsmyren, Jmt</t>
+          <t>Lappungsmyren (leden), Ankarede, Frostviken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>466006</v>
+        <v>465175</v>
       </c>
       <c r="R5" t="n">
-        <v>7187688</v>
+        <v>7187535</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1079,17 +1087,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>I urskogsartad fjällgranskog.</t>
+          <t>Strax O. lokalpunkt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1105,15 +1113,478 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Hammarberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134269163</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lappungsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>465607</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7187378</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ole Jonsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ole Jonsson, Ulf Hansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134269161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lappungsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>465607</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7187378</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ole Jonsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ole Jonsson, Ulf Hansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134269171</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lappungsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>465607</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7187378</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ole Jonsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ole Jonsson, Ulf Hansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119829963</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90668</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>245031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Borgsjömusseron</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tricholoma borgsjoeënse</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Jacobsson &amp; Muskos</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lappungsmyren, Lappungsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>466006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7187688</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I urskogsartad fjällgranskog.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Rashid Kadhim</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61907-2023 artfynd.xlsx
+++ b/artfynd/A 61907-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119828801</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86939718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129151847</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,6 +1142,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129151971</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269163</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269161</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134269171</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1585,8 +1625,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119829963</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>